--- a/ig/ch-core/StructureDefinition-ch-core-immunization.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -473,6 +473,19 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Immunization.extension:indicationCode</t>
+  </si>
+  <si>
+    <t>indicationCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.ch/ig/ch-core/StructureDefinition/ch-ext-epl-regulated-authorization-limitation-indication-code}
+</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
     <t>Immunization.modifierExtension</t>
@@ -1671,12 +1684,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO65"/>
+  <dimension ref="A1:AO66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.25" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.25" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2891,43 +2904,41 @@
         <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>153</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>80</v>
       </c>
@@ -2975,7 +2986,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2984,7 +2995,7 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>141</v>
@@ -3007,14 +3018,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3027,22 +3038,26 @@
         <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3090,7 +3105,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3102,30 +3117,30 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3133,32 +3148,30 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3183,13 +3196,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3207,13 +3220,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -3222,27 +3235,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3250,7 +3263,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
@@ -3259,22 +3272,22 @@
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3300,13 +3313,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3324,10 +3337,10 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>90</v>
@@ -3339,16 +3352,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
@@ -3356,10 +3369,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3367,7 +3380,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
@@ -3379,18 +3392,20 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3415,11 +3430,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3437,10 +3454,10 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>90</v>
@@ -3452,27 +3469,27 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3495,13 +3512,13 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3528,13 +3545,11 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3552,7 +3567,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>90</v>
@@ -3567,27 +3582,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3595,7 +3610,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>90</v>
@@ -3607,16 +3622,16 @@
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3667,10 +3682,10 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>90</v>
@@ -3682,16 +3697,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>80</v>
@@ -3699,10 +3714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3710,7 +3725,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>90</v>
@@ -3722,20 +3737,18 @@
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3784,10 +3797,10 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>90</v>
@@ -3799,27 +3812,27 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>217</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3827,7 +3840,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>90</v>
@@ -3839,18 +3852,20 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3899,10 +3914,10 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>90</v>
@@ -3914,27 +3929,27 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3954,20 +3969,18 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>228</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4016,7 +4029,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4034,13 +4047,13 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
@@ -4048,10 +4061,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4071,19 +4084,19 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>174</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4109,13 +4122,13 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
@@ -4133,7 +4146,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4151,13 +4164,13 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>80</v>
@@ -4165,10 +4178,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4191,15 +4204,17 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4224,13 +4239,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>80</v>
+        <v>241</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4248,7 +4263,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4263,16 +4278,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -4280,10 +4295,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4306,13 +4321,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4363,7 +4378,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4378,27 +4393,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>253</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4421,13 +4436,13 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4478,7 +4493,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4496,24 +4511,24 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4536,13 +4551,13 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4593,7 +4608,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4611,24 +4626,24 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4651,13 +4666,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4684,13 +4699,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4708,7 +4723,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4726,24 +4741,24 @@
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4766,13 +4781,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4799,11 +4814,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -4821,7 +4838,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4839,24 +4856,24 @@
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4879,13 +4896,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4912,13 +4929,11 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -4936,7 +4951,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4954,24 +4969,24 @@
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4982,7 +4997,7 @@
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -4991,16 +5006,16 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5051,13 +5066,13 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
@@ -5066,13 +5081,13 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5083,10 +5098,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5097,7 +5112,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5106,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5166,28 +5181,28 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5198,21 +5213,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5224,17 +5239,15 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5283,28 +5296,28 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5322,7 +5335,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>305</v>
+        <v>153</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5335,26 +5348,24 @@
         <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="N32" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5402,7 +5413,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5423,7 +5434,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>133</v>
+        <v>303</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5434,33 +5445,33 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>310</v>
@@ -5468,8 +5479,12 @@
       <c r="M33" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="N33" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5493,52 +5508,52 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="Y33" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>133</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5549,10 +5564,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5560,7 +5575,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -5575,17 +5590,15 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>318</v>
+        <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5610,13 +5623,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
+        <v>316</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>318</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -5634,10 +5647,10 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -5649,16 +5662,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -5666,10 +5679,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5677,10 +5690,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -5692,15 +5705,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5749,13 +5764,13 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
@@ -5764,16 +5779,16 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -5781,10 +5796,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5804,16 +5819,16 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>330</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5840,13 +5855,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5864,7 +5879,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5879,13 +5894,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5896,10 +5911,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5922,13 +5937,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>178</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5955,13 +5970,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -5979,7 +5994,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5994,13 +6009,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -6025,36 +6040,32 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>225</v>
+        <v>344</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>346</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q38" t="s" s="2">
-        <v>347</v>
-      </c>
+      <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6104,7 +6115,7 @@
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
@@ -6113,10 +6124,10 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>133</v>
@@ -6130,10 +6141,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6144,32 +6155,36 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>174</v>
+        <v>229</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q39" s="2"/>
+      <c r="Q39" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="R39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6189,13 +6204,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>353</v>
+        <v>80</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6213,13 +6228,13 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
@@ -6231,7 +6246,7 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>133</v>
@@ -6245,10 +6260,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6271,13 +6286,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>289</v>
+        <v>178</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6304,13 +6319,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>356</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6328,7 +6343,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6340,7 +6355,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>357</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6374,7 +6389,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6386,13 +6401,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>297</v>
+        <v>360</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6443,19 +6458,19 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>80</v>
+        <v>361</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6464,7 +6479,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>299</v>
+        <v>133</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -6475,21 +6490,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6501,17 +6516,15 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6560,28 +6573,28 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -6592,14 +6605,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>305</v>
+        <v>153</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6612,26 +6625,24 @@
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="N43" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6679,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6700,7 +6711,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>133</v>
+        <v>303</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -6711,42 +6722,46 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>255</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -6794,25 +6809,25 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>133</v>
@@ -6852,7 +6867,7 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>104</v>
+        <v>259</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>366</v>
@@ -6927,7 +6942,7 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>133</v>
@@ -6941,10 +6956,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6967,13 +6982,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7024,7 +7039,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7042,7 +7057,7 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>133</v>
@@ -7082,7 +7097,7 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>373</v>
@@ -7185,7 +7200,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7197,7 +7212,7 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>377</v>
@@ -7230,13 +7245,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7260,7 +7275,7 @@
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
@@ -7272,7 +7287,7 @@
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>133</v>
@@ -7286,10 +7301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7300,7 +7315,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
@@ -7312,13 +7327,13 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7345,13 +7360,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7369,13 +7384,13 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
@@ -7387,7 +7402,7 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>80</v>
+        <v>385</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>133</v>
@@ -7401,10 +7416,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7415,7 +7430,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -7427,17 +7442,15 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>289</v>
+        <v>178</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>390</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7462,13 +7475,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>80</v>
+        <v>389</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>80</v>
+        <v>390</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7486,13 +7499,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -7504,10 +7517,10 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>391</v>
+        <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>392</v>
+        <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -7518,10 +7531,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7532,7 +7545,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7544,15 +7557,17 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>296</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7601,28 +7616,28 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>298</v>
+        <v>391</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>299</v>
+        <v>396</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -7633,21 +7648,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7659,17 +7674,15 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7718,28 +7731,28 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7750,14 +7763,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>305</v>
+        <v>153</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7770,26 +7783,24 @@
         <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -7837,7 +7848,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7858,7 +7869,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>133</v>
+        <v>303</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -7869,42 +7880,46 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>219</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>397</v>
+        <v>310</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -7952,28 +7967,28 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>396</v>
+        <v>312</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>399</v>
+        <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>215</v>
+        <v>133</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8010,13 +8025,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8085,10 +8100,10 @@
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>405</v>
+        <v>219</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -8099,10 +8114,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8125,13 +8140,13 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>225</v>
+        <v>405</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8182,7 +8197,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8200,10 +8215,10 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8214,10 +8229,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8228,7 +8243,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -8240,13 +8255,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8297,13 +8312,13 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
@@ -8315,10 +8330,10 @@
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>80</v>
+        <v>413</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>133</v>
+        <v>414</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -8329,10 +8344,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8343,7 +8358,7 @@
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8355,13 +8370,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>296</v>
+        <v>416</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>297</v>
+        <v>417</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8412,19 +8427,19 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>298</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -8433,7 +8448,7 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>299</v>
+        <v>133</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8444,21 +8459,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -8470,17 +8485,15 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8529,28 +8542,28 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -8561,14 +8574,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>305</v>
+        <v>153</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8581,26 +8594,24 @@
         <v>80</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8648,7 +8659,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8669,7 +8680,7 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>133</v>
+        <v>303</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
@@ -8680,42 +8691,46 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>255</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>418</v>
+        <v>310</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8763,19 +8778,19 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>417</v>
+        <v>312</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
@@ -8795,10 +8810,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8821,13 +8836,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8878,7 +8893,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -8910,10 +8925,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8924,7 +8939,7 @@
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
@@ -8936,13 +8951,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>174</v>
+        <v>252</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8969,13 +8984,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>426</v>
+        <v>80</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -8993,13 +9008,13 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
@@ -9025,10 +9040,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9036,10 +9051,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>80</v>
@@ -9051,17 +9066,15 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L64" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9086,13 +9099,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>80</v>
+        <v>430</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9110,13 +9123,13 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
@@ -9142,10 +9155,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9153,7 +9166,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>90</v>
@@ -9168,7 +9181,7 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>434</v>
@@ -9177,7 +9190,7 @@
         <v>435</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9227,10 +9240,10 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>90</v>
@@ -9254,6 +9267,123 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>80</v>
       </c>
     </row>
